--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484074_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484074_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7383</v>
+        <v>5.5556</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8792</v>
+        <v>6.2476</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1409</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>2.1887</v>
@@ -610,13 +610,13 @@
         <v>2.3806</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1801</v>
+        <v>-0.3628</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9408</v>
+        <v>-0.5723</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2393</v>
+        <v>0.2096</v>
       </c>
       <c r="V2" t="n">
         <v>1.349</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4781</v>
+        <v>3.4748</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3077</v>
+        <v>3.4914</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1704</v>
+        <v>-0.0166</v>
       </c>
       <c r="G3" t="n">
         <v>2.344</v>
@@ -688,13 +688,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7968</v>
+        <v>0.7935</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3604</v>
+        <v>0.5442</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4364</v>
+        <v>0.2494</v>
       </c>
       <c r="V3" t="n">
         <v>0.3373</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4298</v>
+        <v>0.4554</v>
       </c>
       <c r="E4" t="n">
-        <v>0.973</v>
+        <v>1.2791</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5432</v>
+        <v>-0.8238</v>
       </c>
       <c r="G4" t="n">
         <v>0.2777</v>
@@ -766,13 +766,13 @@
         <v>0.9919</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3798</v>
+        <v>-0.3543</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.3174</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2436</v>
+        <v>-0.0369</v>
       </c>
       <c r="V4" t="n">
         <v>0.532</v>
@@ -785,11 +785,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>M. MAÑES CARRETERO</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -799,71 +795,75 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5161</v>
+        <v>-0.0747</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4295</v>
+        <v>0.1732</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.2479</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.835</v>
+        <v>-0.7053</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9631</v>
+        <v>-0.0912</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8719</v>
+        <v>-0.614</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4012</v>
+        <v>0.2015</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0335</v>
+        <v>0.1613</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6324</v>
+        <v>0.0402</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.2362</v>
+        <v>-0.9067</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.9966</v>
+        <v>-0.2525</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2396</v>
+        <v>-0.6542</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7935</v>
+        <v>0.5952</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7855</v>
+        <v>0.5952</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1882</v>
+        <v>0.0354</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.442</v>
+        <v>-0.0283</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6302</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3373</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>. VICENTE SABARIEGO</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8475</v>
+        <v>-0.0747</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.235</v>
+        <v>0.1732</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6126</v>
+        <v>-0.2479</v>
       </c>
       <c r="G6" t="n">
         <v>-0.7053</v>
@@ -918,13 +918,13 @@
         <v>0.5952</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7374000000000001</v>
+        <v>0.0354</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4364</v>
+        <v>-0.0283</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.301</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -939,7 +939,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>. VICENTE SABARIEGO</t>
+          <t>B. GASSAMA KARGBO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -951,73 +951,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8475</v>
+        <v>-0.7000999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.235</v>
+        <v>-0.8057</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6126</v>
+        <v>0.1056</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7053</v>
+        <v>0.2135</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0912</v>
+        <v>0.5995</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.614</v>
+        <v>-0.3861</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2015</v>
+        <v>0.7284</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1613</v>
+        <v>0.0456</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0402</v>
+        <v>0.6827</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9067</v>
+        <v>-0.5149</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2525</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6542</v>
+        <v>-1.0688</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5952</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5952</v>
+        <v>1.1903</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7374000000000001</v>
+        <v>0.146</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4364</v>
+        <v>-0.4194</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.301</v>
+        <v>0.5653</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.8692</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.1352</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. GASSAMA KARGBO</t>
+          <t>M. MAÑES CARRETERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1029,67 +1029,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1629</v>
+        <v>-0.7241</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0721</v>
+        <v>-0.4692</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.2549</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2135</v>
+        <v>-1.835</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5995</v>
+        <v>-0.9631</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3861</v>
+        <v>-0.8719</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7284</v>
+        <v>0.4012</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0456</v>
+        <v>1.0335</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6827</v>
+        <v>-0.6324</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5149</v>
+        <v>-2.2362</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5538999999999999</v>
+        <v>-1.9966</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0688</v>
+        <v>-0.2396</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7935</v>
+        <v>0.7935</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1903</v>
+        <v>1.7855</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3168</v>
+        <v>-0.0199</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6858</v>
+        <v>-0.4817</v>
       </c>
       <c r="U8" t="n">
-        <v>0.369</v>
+        <v>0.4618</v>
       </c>
       <c r="V8" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.6032</v>
+      </c>
+      <c r="X8" t="n">
         <v>-0.266</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.8692</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-1.1352</v>
       </c>
     </row>
     <row r="9">
@@ -1107,13 +1107,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4798</v>
+        <v>-1.9008</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3</v>
+        <v>1.402</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.7798</v>
+        <v>-3.3028</v>
       </c>
       <c r="G9" t="n">
         <v>2.4156</v>
@@ -1152,13 +1152,13 @@
         <v>1.9838</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7645999999999999</v>
+        <v>-0.1856</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1926</v>
+        <v>-0.0906</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.572</v>
+        <v>-0.095</v>
       </c>
       <c r="V9" t="n">
         <v>-2.1469</v>
@@ -1185,13 +1185,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2914</v>
+        <v>-3.7328</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9266</v>
+        <v>-2.6205</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3647</v>
+        <v>-1.1122</v>
       </c>
       <c r="G10" t="n">
         <v>-1.0795</v>
@@ -1230,13 +1230,13 @@
         <v>0.5952</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2794</v>
+        <v>0.2792</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3741</v>
+        <v>-0.068</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0946</v>
+        <v>0.3471</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5437</v>
@@ -1251,7 +1251,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. SERRATACO SANCHEZ</t>
+          <t>E. MAÑES CARRETERO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1263,64 +1263,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6572</v>
+        <v>-5.4516</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4337</v>
+        <v>-3.1937</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2236</v>
+        <v>-2.2579</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.4582</v>
+        <v>-8.794600000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.9762</v>
+        <v>-2.8375</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.482</v>
+        <v>-5.9572</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.2074</v>
+        <v>-4.0751</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.4483</v>
+        <v>-0.6441</v>
       </c>
       <c r="L11" t="n">
-        <v>0.241</v>
+        <v>-3.4309</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.2508</v>
+        <v>-4.7196</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5278</v>
+        <v>-2.1933</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.723</v>
+        <v>-2.5262</v>
       </c>
       <c r="P11" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="Q11" t="n">
         <v>-1.9838</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-3.9677</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.9838</v>
+        <v>2.3806</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5027</v>
+        <v>0.3387</v>
       </c>
       <c r="T11" t="n">
-        <v>0.856</v>
+        <v>-0.3456</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6466</v>
+        <v>0.6843</v>
       </c>
       <c r="V11" t="n">
-        <v>3.2821</v>
+        <v>2.6076</v>
       </c>
       <c r="W11" t="n">
-        <v>3.8854</v>
+        <v>3.2109</v>
       </c>
       <c r="X11" t="n">
         <v>-0.6032</v>
@@ -1329,7 +1329,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. MAÑES CARRETERO</t>
+          <t>S. SERRATACO SANCHEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1341,64 +1341,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9962</v>
+        <v>-5.5973</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6641</v>
+        <v>-4.2896</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3321</v>
+        <v>-1.3077</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.794600000000001</v>
+        <v>-7.4582</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.8375</v>
+        <v>-5.9762</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.9572</v>
+        <v>-1.482</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.0751</v>
+        <v>-4.2074</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6441</v>
+        <v>-4.4483</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.4309</v>
+        <v>0.241</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.7196</v>
+        <v>-3.2508</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.1933</v>
+        <v>-1.5278</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.5262</v>
+        <v>-1.723</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3968</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9838</v>
+        <v>-3.9677</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3806</v>
+        <v>1.9838</v>
       </c>
       <c r="S12" t="n">
-        <v>0.794</v>
+        <v>0.5626</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8161</v>
+        <v>0.0001</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6101</v>
+        <v>0.5625</v>
       </c>
       <c r="V12" t="n">
-        <v>2.6076</v>
+        <v>3.2821</v>
       </c>
       <c r="W12" t="n">
-        <v>3.2109</v>
+        <v>3.8854</v>
       </c>
       <c r="X12" t="n">
         <v>-0.6032</v>
@@ -1419,13 +1419,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.1524</v>
+        <v>-8.770299999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4638999999999984</v>
+        <v>1.3878</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.6164</v>
+        <v>-10.1581</v>
       </c>
       <c r="G13" t="n">
         <v>-13.1384</v>
@@ -1437,7 +1437,7 @@
         <v>-6.6707</v>
       </c>
       <c r="J13" t="n">
-        <v>8.564199999999996</v>
+        <v>8.5642</v>
       </c>
       <c r="K13" t="n">
         <v>4.022600000000001</v>
@@ -1455,7 +1455,7 @@
         <v>-11.2123</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.3885</v>
+        <v>-1.388500000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-15.8706</v>
@@ -1464,13 +1464,13 @@
         <v>14.4821</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1137999999999999</v>
+        <v>1.2682</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.7313</v>
+        <v>-1.8073</v>
       </c>
       <c r="U13" t="n">
-        <v>2.6172</v>
+        <v>3.0755</v>
       </c>
       <c r="V13" t="n">
         <v>4.4887</v>
@@ -1497,13 +1497,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.8027</v>
+        <v>8.8255</v>
       </c>
       <c r="E14" t="n">
-        <v>10.4109</v>
+        <v>11.1251</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.6082</v>
+        <v>-2.2996</v>
       </c>
       <c r="G14" t="n">
         <v>7.5346</v>
@@ -1542,13 +1542,13 @@
         <v>1.3887</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8258</v>
+        <v>0.197</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8615</v>
+        <v>-0.1473</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0357</v>
+        <v>0.3443</v>
       </c>
       <c r="V14" t="n">
         <v>1.689</v>
@@ -1575,13 +1575,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.574</v>
+        <v>7.4617</v>
       </c>
       <c r="E15" t="n">
         <v>7.0551</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5189</v>
+        <v>0.4066</v>
       </c>
       <c r="G15" t="n">
         <v>8.512</v>
@@ -1620,13 +1620,13 @@
         <v>1.9838</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1746</v>
+        <v>0.0623</v>
       </c>
       <c r="T15" t="n">
         <v>-0.1813</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3559</v>
+        <v>0.2436</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1206</v>
@@ -1653,13 +1653,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5752</v>
+        <v>1.9452</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5239</v>
+        <v>1.8097</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0513</v>
+        <v>0.1355</v>
       </c>
       <c r="G16" t="n">
         <v>1.0737</v>
@@ -1698,13 +1698,13 @@
         <v>0.5952</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9064</v>
+        <v>0.2764</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9863</v>
+        <v>0.2721</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0799</v>
+        <v>0.0042</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1731,13 +1731,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.744</v>
+        <v>1.1623</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1253</v>
+        <v>0.1808</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8692</v>
+        <v>0.9815</v>
       </c>
       <c r="G17" t="n">
         <v>0.9145</v>
@@ -1776,13 +1776,13 @@
         <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2483</v>
+        <v>0.17</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3627</v>
+        <v>-0.0566</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1145</v>
+        <v>0.2267</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1206</v>
@@ -1797,7 +1797,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. TEJERO CASASAYAS</t>
+          <t>A. BALTÀ CASTELLTORT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1809,73 +1809,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0067</v>
+        <v>0.1722</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4847</v>
+        <v>1.1157</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4914</v>
+        <v>-0.9435</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.0113</v>
+        <v>3.4321</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4385</v>
+        <v>3.8855</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5728</v>
+        <v>-0.4534</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1208</v>
+        <v>3.7291</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0764</v>
+        <v>3.5283</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.1972</v>
+        <v>0.2008</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8905</v>
+        <v>-0.297</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5148</v>
+        <v>0.3572</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3756</v>
+        <v>-0.6542</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9919</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9838</v>
+        <v>1.7855</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0973</v>
+        <v>-1.0571</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5667</v>
+        <v>-0.8955</v>
       </c>
       <c r="U18" t="n">
-        <v>1.664</v>
+        <v>-0.1616</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.0713</v>
+        <v>-2.0044</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1947</v>
+        <v>0.266</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.266</v>
+        <v>-2.2704</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BALTÀ CASTELLTORT</t>
+          <t>M. BENITO MULLERAT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1887,73 +1887,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0982</v>
+        <v>-0.7167</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0137</v>
+        <v>-0.2985</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1119</v>
+        <v>-0.4182</v>
       </c>
       <c r="G19" t="n">
-        <v>3.4321</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>3.8855</v>
+        <v>-0.0108</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4534</v>
+        <v>0.9186</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7291</v>
+        <v>1.7934</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5283</v>
+        <v>0.2271</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2008</v>
+        <v>1.5663</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.297</v>
+        <v>-0.8856000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3572</v>
+        <v>-0.2379</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6542</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1984</v>
+        <v>0.9919</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7855</v>
+        <v>1.9838</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3275</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.6914</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3299</v>
+        <v>-0.044</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.0044</v>
+        <v>-1.881</v>
       </c>
       <c r="W19" t="n">
-        <v>0.266</v>
+        <v>-0.4085</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.2704</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. BENITO MULLERAT</t>
+          <t>E. TEJERO CASASAYAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1965,40 +1965,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9692</v>
+        <v>-0.7789</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2985</v>
+        <v>-2.4847</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6707</v>
+        <v>1.7058</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9078000000000001</v>
+        <v>-2.0113</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0108</v>
+        <v>-0.4385</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9186</v>
+        <v>-1.5728</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7934</v>
+        <v>-1.1208</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2271</v>
+        <v>0.0764</v>
       </c>
       <c r="L20" t="n">
-        <v>1.5663</v>
+        <v>-1.1972</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8856000000000001</v>
+        <v>-0.8905</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2379</v>
+        <v>-0.5148</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.3756</v>
       </c>
       <c r="P20" t="n">
         <v>0.9919</v>
@@ -2010,28 +2010,28 @@
         <v>1.9838</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9879</v>
+        <v>0.3117</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6914</v>
+        <v>-0.5667</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2965</v>
+        <v>0.8784</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.881</v>
+        <v>-0.0713</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.4085</v>
+        <v>0.1947</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4724</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. BERNADÍ VALLS</t>
+          <t>A. CUMELLES CESPEDES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2043,73 +2043,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9845</v>
+        <v>-2.5477</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.2873</v>
+        <v>-0.131</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3029</v>
+        <v>-2.4167</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.5718</v>
+        <v>-1.0734</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.4282</v>
+        <v>0.2273</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8564000000000001</v>
+        <v>-1.3007</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.0878</v>
+        <v>0.2577</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.251</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1632</v>
+        <v>-0.64</v>
       </c>
       <c r="M21" t="n">
-        <v>0.516</v>
+        <v>-1.3311</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1772</v>
+        <v>-0.6704</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6932</v>
+        <v>-0.6607</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9838</v>
+        <v>0.5952</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7675</v>
+        <v>0.129</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3119</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4556</v>
+        <v>0.1289</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8198</v>
+        <v>-1.2065</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4724</v>
+        <v>0.6032</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6526</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. CUMELLES CESPEDES</t>
+          <t>M. BERNADÍ VALLS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2121,67 +2121,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2136</v>
+        <v>-2.5507</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1751</v>
+        <v>-4.7975</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3887</v>
+        <v>2.2467</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0734</v>
+        <v>-3.5718</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2273</v>
+        <v>-4.4282</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3007</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2577</v>
+        <v>-4.0878</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8977000000000001</v>
+        <v>-4.251</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.64</v>
+        <v>0.1632</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3311</v>
+        <v>0.516</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6704</v>
+        <v>-0.1772</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6607</v>
+        <v>0.6932</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3968</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5952</v>
+        <v>1.9838</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4631</v>
+        <v>0.2012</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3061</v>
+        <v>-0.1983</v>
       </c>
       <c r="U22" t="n">
-        <v>0.157</v>
+        <v>0.3995</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2065</v>
+        <v>0.8198</v>
       </c>
       <c r="W22" t="n">
-        <v>0.6032</v>
+        <v>1.4724</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.8097</v>
+        <v>-0.6526</v>
       </c>
     </row>
     <row r="23">
@@ -2199,13 +2199,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1322</v>
+        <v>-3.668</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.9791</v>
+        <v>-3.571</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1531</v>
+        <v>-0.097</v>
       </c>
       <c r="G23" t="n">
         <v>-3.285</v>
@@ -2244,13 +2244,13 @@
         <v>2.3806</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6428</v>
+        <v>-0.1786</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8615</v>
+        <v>-0.4534</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2187</v>
+        <v>0.2748</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5931</v>
@@ -2277,19 +2277,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>9.304900000000004</v>
+        <v>9.3049</v>
       </c>
       <c r="E24" t="n">
-        <v>10.0038</v>
+        <v>10.0037</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6988999999999999</v>
+        <v>-0.6988999999999996</v>
       </c>
       <c r="G24" t="n">
         <v>12.4332</v>
       </c>
       <c r="H24" t="n">
-        <v>6.376299999999999</v>
+        <v>6.376300000000001</v>
       </c>
       <c r="I24" t="n">
         <v>6.056699999999999</v>
@@ -2322,19 +2322,19 @@
         <v>15.8707</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6234</v>
+        <v>-0.6234999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.9183</v>
+        <v>-2.9184</v>
       </c>
       <c r="U24" t="n">
-        <v>2.2951</v>
+        <v>2.2948</v>
       </c>
       <c r="V24" t="n">
         <v>-4.4887</v>
       </c>
       <c r="W24" t="n">
-        <v>6.0132</v>
+        <v>6.013199999999999</v>
       </c>
       <c r="X24" t="n">
         <v>-10.5017</v>
